--- a/ControlPanels/Event Numbering.xlsx
+++ b/ControlPanels/Event Numbering.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinerpointslimited-my.sharepoint.com/personal/nick_locke_21jubileepark_com/Documents/Model Railway V2/Documentation/RoxeterModelRailway/ControlPanels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dinerpointslimited-my.sharepoint.com/personal/nick_locke_21jubileepark_com/Documents/Model Railway V2/Documentation/RoxeterDocumentation/ControlPanels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="251" documentId="11_F25DC773A252ABDACC10481819195FD05ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB33027-E72A-4D72-B5DD-9023698E61F5}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="11_F25DC773A252ABDACC10481819195FD05ADE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{287425AE-21A9-41F4-8455-361A89D6F20D}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="1440" windowWidth="22740" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31410" yWindow="1500" windowWidth="18225" windowHeight="13785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="91">
   <si>
     <t>Event Groups</t>
   </si>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>As High Byte</t>
-  </si>
-  <si>
-    <t>All signals on</t>
   </si>
   <si>
     <t>Request Status</t>
@@ -1309,7 +1306,7 @@
         <v>0x0F</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
@@ -2525,7 +2522,7 @@
         <v>0x0F</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G50" s="3">
         <f t="shared" si="2"/>
@@ -3161,7 +3158,7 @@
         <v>0x04</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D67" s="3">
         <v>0</v>
@@ -3171,7 +3168,7 @@
         <v>0x00</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G67" s="3">
         <f t="shared" ref="G67:G82" si="6">A67*16+D67</f>
@@ -3199,7 +3196,7 @@
         <v>0x04</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
@@ -3209,7 +3206,7 @@
         <v>0x01</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G68" s="3">
         <f t="shared" si="6"/>
@@ -3237,7 +3234,7 @@
         <v>0x04</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D69" s="3">
         <v>2</v>
@@ -3247,7 +3244,7 @@
         <v>0x02</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G69" s="3">
         <f t="shared" si="6"/>
@@ -3275,7 +3272,7 @@
         <v>0x04</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
@@ -3285,7 +3282,7 @@
         <v>0x03</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G70" s="3">
         <f t="shared" si="6"/>
@@ -3313,7 +3310,7 @@
         <v>0x04</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D71" s="3">
         <v>4</v>
@@ -3323,7 +3320,7 @@
         <v>0x04</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G71" s="3">
         <f t="shared" si="6"/>
@@ -3351,7 +3348,7 @@
         <v>0x04</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D72" s="3">
         <v>5</v>
@@ -3389,7 +3386,7 @@
         <v>0x04</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" s="3">
         <v>6</v>
@@ -3427,7 +3424,7 @@
         <v>0x04</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D74" s="3">
         <v>7</v>
@@ -3465,7 +3462,7 @@
         <v>0x04</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D75" s="3">
         <v>8</v>
@@ -3503,7 +3500,7 @@
         <v>0x04</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D76" s="3">
         <v>9</v>
@@ -3541,7 +3538,7 @@
         <v>0x04</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D77" s="3">
         <v>10</v>
@@ -3579,7 +3576,7 @@
         <v>0x04</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D78" s="3">
         <v>11</v>
@@ -3617,7 +3614,7 @@
         <v>0x04</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D79" s="3">
         <v>12</v>
@@ -3655,7 +3652,7 @@
         <v>0x04</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D80" s="3">
         <v>13</v>
@@ -3693,7 +3690,7 @@
         <v>0x04</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D81" s="3">
         <v>14</v>
@@ -3731,7 +3728,7 @@
         <v>0x04</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D82" s="3">
         <v>15</v>
@@ -3769,7 +3766,7 @@
         <v>0x05</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D83" s="3">
         <v>0</v>
@@ -3779,7 +3776,7 @@
         <v>0x00</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G83" s="3">
         <f t="shared" ref="G83:G98" si="12">A83*16+D83</f>
@@ -3807,7 +3804,7 @@
         <v>0x05</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
@@ -3817,7 +3814,7 @@
         <v>0x01</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G84" s="3">
         <f t="shared" si="12"/>
@@ -3845,7 +3842,7 @@
         <v>0x05</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D85" s="3">
         <v>2</v>
@@ -3855,7 +3852,7 @@
         <v>0x02</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G85" s="3">
         <f t="shared" si="12"/>
@@ -3883,7 +3880,7 @@
         <v>0x05</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D86" s="3">
         <v>3</v>
@@ -3893,7 +3890,7 @@
         <v>0x03</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G86" s="3">
         <f t="shared" si="12"/>
@@ -3921,7 +3918,7 @@
         <v>0x05</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D87" s="3">
         <v>4</v>
@@ -3931,7 +3928,7 @@
         <v>0x04</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G87" s="3">
         <f t="shared" si="12"/>
@@ -3959,7 +3956,7 @@
         <v>0x05</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D88" s="3">
         <v>5</v>
@@ -3969,7 +3966,7 @@
         <v>0x05</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G88" s="3">
         <f t="shared" si="12"/>
@@ -3997,7 +3994,7 @@
         <v>0x05</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D89" s="3">
         <v>6</v>
@@ -4007,7 +4004,7 @@
         <v>0x06</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G89" s="3">
         <f t="shared" si="12"/>
@@ -4035,7 +4032,7 @@
         <v>0x05</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D90" s="3">
         <v>7</v>
@@ -4045,7 +4042,7 @@
         <v>0x07</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G90" s="3">
         <f t="shared" si="12"/>
@@ -4073,7 +4070,7 @@
         <v>0x05</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D91" s="3">
         <v>8</v>
@@ -4083,7 +4080,7 @@
         <v>0x08</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G91" s="3">
         <f t="shared" si="12"/>
@@ -4111,7 +4108,7 @@
         <v>0x05</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D92" s="3">
         <v>9</v>
@@ -4149,7 +4146,7 @@
         <v>0x05</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D93" s="3">
         <v>10</v>
@@ -4159,7 +4156,7 @@
         <v>0x0A</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G93" s="3">
         <f t="shared" si="12"/>
@@ -4187,7 +4184,7 @@
         <v>0x05</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D94" s="3">
         <v>11</v>
@@ -4197,7 +4194,7 @@
         <v>0x0B</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G94" s="3">
         <f t="shared" si="12"/>
@@ -4225,7 +4222,7 @@
         <v>0x05</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D95" s="3">
         <v>12</v>
@@ -4235,7 +4232,7 @@
         <v>0x0C</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G95" s="3">
         <f t="shared" si="12"/>
@@ -4263,7 +4260,7 @@
         <v>0x05</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D96" s="3">
         <v>13</v>
@@ -4273,7 +4270,7 @@
         <v>0x0D</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G96" s="3">
         <f t="shared" si="12"/>
@@ -4301,7 +4298,7 @@
         <v>0x05</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D97" s="3">
         <v>14</v>
@@ -4311,7 +4308,7 @@
         <v>0x0E</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G97" s="3">
         <f t="shared" si="12"/>
@@ -4339,7 +4336,7 @@
         <v>0x05</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D98" s="3">
         <v>15</v>
@@ -4349,7 +4346,7 @@
         <v>0x0F</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G98" s="3">
         <f t="shared" si="12"/>
